--- a/Monthly_Breakout_Report.xlsx
+++ b/Monthly_Breakout_Report.xlsx
@@ -523,7 +523,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Monthly Breakout Screener  —  Generated: 23 May 2026 09:18 IST</t>
+          <t>NSE Monthly Breakout Screener  —  Generated: 23 May 2026 09:40 IST</t>
         </is>
       </c>
     </row>

--- a/Monthly_Breakout_Report.xlsx
+++ b/Monthly_Breakout_Report.xlsx
@@ -523,7 +523,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Monthly Breakout Screener  —  Generated: 23 May 2026 09:40 IST</t>
+          <t>NSE Monthly Breakout Screener  —  Generated: 23 May 2026 10:10 IST</t>
         </is>
       </c>
     </row>

--- a/Monthly_Breakout_Report.xlsx
+++ b/Monthly_Breakout_Report.xlsx
@@ -523,7 +523,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Monthly Breakout Screener  —  Generated: 23 May 2026 10:10 IST</t>
+          <t>NSE Monthly Breakout Screener  —  Generated: 23 May 2026 10:17 IST</t>
         </is>
       </c>
     </row>

--- a/Monthly_Breakout_Report.xlsx
+++ b/Monthly_Breakout_Report.xlsx
@@ -523,7 +523,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Monthly Breakout Screener  —  Generated: 01 Jun 2026 15:20 IST</t>
+          <t>NSE Monthly Breakout Screener  —  Generated: 01 Jun 2026 16:24 IST</t>
         </is>
       </c>
     </row>
